--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M288"/>
+  <dimension ref="A1:M286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23153277.84</v>
+        <v>25793.56</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>242760</v>
+        <v>270.44</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7557660.25</v>
+        <v>8419.5</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>878220</v>
+        <v>978.37</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15237683.44</v>
+        <v>16975.31</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>250754.42</v>
+        <v>279.35</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15979967.36</v>
+        <v>17802.24</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>28505188.6</v>
+        <v>31755.78</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>679055.65</v>
+        <v>756.49</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1499400</v>
+        <v>1670.38</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>424023.18</v>
+        <v>472.38</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8673.43</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>921452.7</v>
+        <v>1026.53</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>600134.85</v>
+        <v>668.5700000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7938.94</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>203462.63</v>
+        <v>226.66</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>874891.5699999999</v>
+        <v>974.66</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>594069.42</v>
+        <v>661.8099999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8619.32</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4729357.5</v>
+        <v>5268.67</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12879132</v>
+        <v>14347.8</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7618841.72</v>
+        <v>8487.66</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15114508.92</v>
+        <v>16838.09</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1714534.15</v>
+        <v>1910.05</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1067176.53</v>
+        <v>1188.87</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8419.049999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>781352.8100000001</v>
+        <v>870.45</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>274735.3</v>
+        <v>306.06</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8419.049999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>572983.8100000001</v>
+        <v>638.3200000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>841773.87</v>
+        <v>937.77</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>323495.55</v>
+        <v>360.39</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>8417735.130000001</v>
+        <v>9377.65</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>621290.67</v>
+        <v>692.14</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7142453.78</v>
+        <v>7956.94</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9498580</v>
+        <v>10581.75</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>21606318.3</v>
+        <v>24070.19</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1149460.27</v>
+        <v>1280.54</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>624846.39</v>
+        <v>696.1</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>250754.42</v>
+        <v>279.35</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2225366.64</v>
+        <v>2479.14</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>188041.42</v>
+        <v>209.48</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8419.049999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>15979967.36</v>
+        <v>17802.24</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1199758</v>
+        <v>1336.57</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2519468</v>
+        <v>2806.78</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>409360</v>
+        <v>456.04</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10524360</v>
+        <v>11724.5</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1749276.2</v>
+        <v>1948.75</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>462443.52</v>
+        <v>515.1799999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8619.32</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1083315.31</v>
+        <v>1206.85</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7618841.72</v>
+        <v>8487.66</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7938.94</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2383712.8</v>
+        <v>2655.54</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6390169.1</v>
+        <v>7118.87</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1154776</v>
+        <v>1286.46</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3184142.5</v>
+        <v>3547.25</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4578168</v>
+        <v>5100.24</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>16985210.34</v>
+        <v>18922.12</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2298524.27</v>
+        <v>2560.64</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>14394899.26</v>
+        <v>16036.42</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>173804.26</v>
+        <v>193.62</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7618841.72</v>
+        <v>8487.66</v>
       </c>
     </row>
     <row r="66">
@@ -4469,11 +4469,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>28505188.6</v>
+        <v>31755.78</v>
       </c>
     </row>
     <row r="67">
@@ -4530,11 +4530,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>815850.91</v>
+        <v>908.89</v>
       </c>
     </row>
     <row r="68">
@@ -4591,11 +4591,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8018.21</v>
       </c>
     </row>
     <row r="69">
@@ -4652,11 +4652,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2483958.4</v>
+        <v>2767.22</v>
       </c>
     </row>
     <row r="70">
@@ -4713,11 +4713,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>28700985.25</v>
+        <v>31973.9</v>
       </c>
     </row>
     <row r="71">
@@ -4774,11 +4774,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>833887.74</v>
+        <v>928.98</v>
       </c>
     </row>
     <row r="72">
@@ -4835,11 +4835,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4932288.2</v>
+        <v>5494.74</v>
       </c>
     </row>
     <row r="73">
@@ -4896,11 +4896,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>96889.8</v>
+        <v>107.94</v>
       </c>
     </row>
     <row r="74">
@@ -4957,11 +4957,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>762318.76</v>
+        <v>849.25</v>
       </c>
     </row>
     <row r="75">
@@ -5018,11 +5018,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>510111.35</v>
+        <v>568.28</v>
       </c>
     </row>
     <row r="76">
@@ -5079,11 +5079,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8018.21</v>
       </c>
     </row>
     <row r="77">
@@ -5140,11 +5140,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>610700.86</v>
+        <v>680.34</v>
       </c>
     </row>
     <row r="78">
@@ -5201,11 +5201,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8204186.06</v>
+        <v>9139.75</v>
       </c>
     </row>
     <row r="79">
@@ -5262,11 +5262,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>801630.41</v>
+        <v>893.04</v>
       </c>
     </row>
     <row r="80">
@@ -5323,11 +5323,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>869355.6899999999</v>
+        <v>968.49</v>
       </c>
     </row>
     <row r="81">
@@ -5384,11 +5384,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7938.94</v>
       </c>
     </row>
     <row r="82">
@@ -5445,11 +5445,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8673.43</v>
       </c>
     </row>
     <row r="83">
@@ -5506,11 +5506,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8204186.06</v>
+        <v>9139.75</v>
       </c>
     </row>
     <row r="84">
@@ -5567,11 +5567,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>529523.8199999999</v>
+        <v>589.91</v>
       </c>
     </row>
     <row r="85">
@@ -5628,11 +5628,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7938.94</v>
       </c>
     </row>
     <row r="86">
@@ -5689,11 +5689,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>298950.61</v>
+        <v>333.04</v>
       </c>
     </row>
     <row r="87">
@@ -5750,11 +5750,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>15483780.2</v>
+        <v>17249.47</v>
       </c>
     </row>
     <row r="88">
@@ -5811,11 +5811,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>287211.26</v>
+        <v>319.96</v>
       </c>
     </row>
     <row r="89">
@@ -5872,11 +5872,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>14252594.3</v>
+        <v>15877.89</v>
       </c>
     </row>
     <row r="90">
@@ -5933,11 +5933,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1076149.13</v>
+        <v>1198.87</v>
       </c>
     </row>
     <row r="91">
@@ -5994,11 +5994,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>134978.13</v>
+        <v>150.37</v>
       </c>
     </row>
     <row r="92">
@@ -6055,11 +6055,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8018.21</v>
       </c>
     </row>
     <row r="93">
@@ -6116,11 +6116,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1551235.21</v>
+        <v>1728.13</v>
       </c>
     </row>
     <row r="94">
@@ -6177,11 +6177,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>14252594.3</v>
+        <v>15877.89</v>
       </c>
     </row>
     <row r="95">
@@ -6238,11 +6238,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2369284.05</v>
+        <v>2639.47</v>
       </c>
     </row>
     <row r="96">
@@ -6299,11 +6299,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>782101.3199999999</v>
+        <v>871.29</v>
       </c>
     </row>
     <row r="97">
@@ -6360,11 +6360,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1043589.54</v>
+        <v>1162.6</v>
       </c>
     </row>
     <row r="98">
@@ -6421,11 +6421,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2297556.8</v>
+        <v>2559.56</v>
       </c>
     </row>
     <row r="99">
@@ -6482,11 +6482,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3280354</v>
+        <v>3654.43</v>
       </c>
     </row>
     <row r="100">
@@ -6543,11 +6543,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>910380.9399999999</v>
+        <v>1014.2</v>
       </c>
     </row>
     <row r="101">
@@ -6604,11 +6604,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>548501.9399999999</v>
+        <v>611.05</v>
       </c>
     </row>
     <row r="102">
@@ -6665,11 +6665,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>494683</v>
+        <v>551.09</v>
       </c>
     </row>
     <row r="103">
@@ -6726,11 +6726,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8619.32</v>
       </c>
     </row>
     <row r="104">
@@ -6787,11 +6787,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8018.21</v>
       </c>
     </row>
     <row r="105">
@@ -6848,11 +6848,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1024091.39</v>
+        <v>1140.87</v>
       </c>
     </row>
     <row r="106">
@@ -6909,11 +6909,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>534408.77</v>
+        <v>595.35</v>
       </c>
     </row>
     <row r="107">
@@ -6970,11 +6970,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8619.32</v>
       </c>
     </row>
     <row r="108">
@@ -7031,11 +7031,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>614256.58</v>
+        <v>684.3</v>
       </c>
     </row>
     <row r="109">
@@ -7092,11 +7092,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>567845.39</v>
+        <v>632.6</v>
       </c>
     </row>
     <row r="110">
@@ -7153,11 +7153,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>907279.8</v>
+        <v>1010.74</v>
       </c>
     </row>
     <row r="111">
@@ -7214,11 +7214,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>7197449.63</v>
+        <v>8018.21</v>
       </c>
     </row>
     <row r="112">
@@ -7275,11 +7275,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>673447.1800000001</v>
+        <v>750.24</v>
       </c>
     </row>
     <row r="113">
@@ -7336,11 +7336,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>462057.96</v>
+        <v>514.75</v>
       </c>
     </row>
     <row r="114">
@@ -7397,11 +7397,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="115">
@@ -7458,11 +7458,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>566939.8</v>
+        <v>631.59</v>
       </c>
     </row>
     <row r="116">
@@ -7519,11 +7519,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8204186.06</v>
+        <v>9139.75</v>
       </c>
     </row>
     <row r="117">
@@ -7580,11 +7580,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>718506.53</v>
+        <v>800.4400000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7641,11 +7641,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6917850.8</v>
+        <v>7706.73</v>
       </c>
     </row>
     <row r="119">
@@ -7702,11 +7702,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7763,11 +7763,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7824,11 +7824,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7885,11 +7885,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>807514.96</v>
+        <v>899.6</v>
       </c>
     </row>
     <row r="123">
@@ -7946,11 +7946,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>249233.6</v>
+        <v>277.65</v>
       </c>
     </row>
     <row r="124">
@@ -8007,11 +8007,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2891700</v>
+        <v>3221.45</v>
       </c>
     </row>
     <row r="125">
@@ -8068,11 +8068,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1710590.49</v>
+        <v>1905.66</v>
       </c>
     </row>
     <row r="126">
@@ -8129,11 +8129,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7938.94</v>
       </c>
     </row>
     <row r="127">
@@ -8190,11 +8190,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>8568359.380000001</v>
+        <v>9545.450000000001</v>
       </c>
     </row>
     <row r="128">
@@ -8251,11 +8251,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3798796.54</v>
+        <v>4231.99</v>
       </c>
     </row>
     <row r="129">
@@ -8312,11 +8312,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2486562.12</v>
+        <v>2770.12</v>
       </c>
     </row>
     <row r="130">
@@ -8373,11 +8373,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2195288.2</v>
+        <v>2445.63</v>
       </c>
     </row>
     <row r="131">
@@ -8434,11 +8434,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>6518117.9</v>
+        <v>7261.41</v>
       </c>
     </row>
     <row r="132">
@@ -8495,11 +8495,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4582452</v>
+        <v>5105.01</v>
       </c>
     </row>
     <row r="133">
@@ -8556,11 +8556,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4582452</v>
+        <v>5105.01</v>
       </c>
     </row>
     <row r="134">
@@ -8617,11 +8617,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4582452</v>
+        <v>5105.01</v>
       </c>
     </row>
     <row r="135">
@@ -8678,11 +8678,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4634931</v>
+        <v>5163.48</v>
       </c>
     </row>
     <row r="136">
@@ -8739,11 +8739,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>135636.2</v>
+        <v>151.1</v>
       </c>
     </row>
     <row r="137">
@@ -8800,11 +8800,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>114525.6</v>
+        <v>127.59</v>
       </c>
     </row>
     <row r="138">
@@ -8861,11 +8861,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>8700168.539999999</v>
+        <v>9692.290000000001</v>
       </c>
     </row>
     <row r="139">
@@ -8922,11 +8922,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>519916.95</v>
+        <v>579.21</v>
       </c>
     </row>
     <row r="140">
@@ -8983,11 +8983,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>4582452</v>
+        <v>5105.01</v>
       </c>
     </row>
     <row r="141">
@@ -9044,11 +9044,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>496577.48</v>
+        <v>553.2</v>
       </c>
     </row>
     <row r="142">
@@ -9105,11 +9105,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>14252594.3</v>
+        <v>15877.89</v>
       </c>
     </row>
     <row r="143">
@@ -9166,11 +9166,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>817449.08</v>
+        <v>910.67</v>
       </c>
     </row>
     <row r="144">
@@ -9227,11 +9227,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7938.94</v>
       </c>
     </row>
     <row r="145">
@@ -9288,11 +9288,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1280417.39</v>
+        <v>1426.43</v>
       </c>
     </row>
     <row r="146">
@@ -9349,11 +9349,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1221822.98</v>
+        <v>1361.15</v>
       </c>
     </row>
     <row r="147">
@@ -9410,11 +9410,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>761945.1</v>
+        <v>848.83</v>
       </c>
     </row>
     <row r="148">
@@ -9471,11 +9471,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>626326.75</v>
+        <v>697.75</v>
       </c>
     </row>
     <row r="149">
@@ -9532,11 +9532,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="150">
@@ -9593,11 +9593,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>626326.75</v>
+        <v>697.75</v>
       </c>
     </row>
     <row r="151">
@@ -9654,11 +9654,11 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>14396422.46</v>
+        <v>16038.12</v>
       </c>
     </row>
     <row r="152">
@@ -9715,11 +9715,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1227767.03</v>
+        <v>1367.78</v>
       </c>
     </row>
     <row r="153">
@@ -9776,11 +9776,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="154">
@@ -9837,11 +9837,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>808915.59</v>
+        <v>901.16</v>
       </c>
     </row>
     <row r="155">
@@ -9898,11 +9898,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>14252594.3</v>
+        <v>15877.89</v>
       </c>
     </row>
     <row r="156">
@@ -9959,11 +9959,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>621321.61</v>
+        <v>692.17</v>
       </c>
     </row>
     <row r="157">
@@ -10020,17 +10020,17 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>758-357-CM26</t>
+          <t>758-355-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10070,22 +10070,22 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2490432</v>
+        <v>540.11</v>
       </c>
     </row>
     <row r="159">
@@ -10142,11 +10142,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="160">
@@ -10203,11 +10203,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>521799.53</v>
+        <v>581.3</v>
       </c>
     </row>
     <row r="161">
@@ -10264,11 +10264,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>832685.84</v>
+        <v>927.64</v>
       </c>
     </row>
     <row r="162">
@@ -10325,17 +10325,17 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>669791.5</v>
+        <v>746.17</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>758-355-CM26</t>
+          <t>758-357-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10375,22 +10375,22 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>484826.23</v>
+        <v>2774.43</v>
       </c>
     </row>
     <row r="164">
@@ -10447,11 +10447,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1841644</v>
+        <v>2051.66</v>
       </c>
     </row>
     <row r="165">
@@ -10508,11 +10508,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4441080</v>
+        <v>4947.52</v>
       </c>
     </row>
     <row r="166">
@@ -10569,11 +10569,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2497929</v>
+        <v>2782.78</v>
       </c>
     </row>
     <row r="167">
@@ -10630,11 +10630,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>7187588.1</v>
+        <v>8007.22</v>
       </c>
     </row>
     <row r="168">
@@ -10691,11 +10691,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1804516</v>
+        <v>2010.29</v>
       </c>
     </row>
     <row r="169">
@@ -10752,11 +10752,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2149044.8</v>
+        <v>2394.11</v>
       </c>
     </row>
     <row r="170">
@@ -10813,11 +10813,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>705372.5</v>
+        <v>785.8099999999999</v>
       </c>
     </row>
     <row r="171">
@@ -10874,11 +10874,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>19037637.85</v>
+        <v>21208.59</v>
       </c>
     </row>
     <row r="172">
@@ -10935,17 +10935,17 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1776432</v>
+        <v>1979.01</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2765-204-CM26</t>
+          <t>2765-206-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10985,28 +10985,28 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8425414.199999999</v>
+        <v>5699.99</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2765-206-CM26</t>
+          <t>2765-204-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -11046,28 +11046,28 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>5116524</v>
+        <v>9386.209999999999</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1078078-1402-CM26</t>
+          <t>1078078-1401-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11118,17 +11118,17 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>397932.43</v>
+        <v>5913.61</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1078078-1401-CM26</t>
+          <t>1078078-1390-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -11168,28 +11168,28 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>5308284.17</v>
+        <v>865.91</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1078078-1390-CM26</t>
+          <t>1078078-1398-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11240,17 +11240,17 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>777272.3</v>
+        <v>1324.28</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1078078-1398-CM26</t>
+          <t>1078078-1397-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11290,28 +11290,28 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1188721.94</v>
+        <v>8019.06</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1078078-1397-CM26</t>
+          <t>1078078-1396-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11351,28 +11351,28 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7198211.23</v>
+        <v>272.56</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1078078-1396-CM26</t>
+          <t>1078078-1394-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11412,28 +11412,28 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>244660.43</v>
+        <v>1166.13</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1078078-1393-CM26</t>
+          <t>1078078-1392-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11473,28 +11473,28 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>15114508.92</v>
+        <v>963.34</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1078078-1392-CM26</t>
+          <t>1078078-1391-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11534,28 +11534,28 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>864727.78</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1078078-1391-CM26</t>
+          <t>1078078-1402-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -11595,22 +11595,22 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>7604124.99</v>
+        <v>443.31</v>
       </c>
     </row>
     <row r="184">
@@ -11667,11 +11667,11 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="185">
@@ -11728,11 +11728,11 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>13997845.05</v>
+        <v>15594.09</v>
       </c>
     </row>
     <row r="186">
@@ -11789,11 +11789,11 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="187">
@@ -11850,11 +11850,11 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>665057.6800000001</v>
+        <v>740.9</v>
       </c>
     </row>
     <row r="188">
@@ -11911,11 +11911,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4638620</v>
+        <v>5167.58</v>
       </c>
     </row>
     <row r="189">
@@ -11972,11 +11972,11 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>24474135</v>
+        <v>27265.04</v>
       </c>
     </row>
     <row r="190">
@@ -12033,11 +12033,11 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="191">
@@ -12094,17 +12094,17 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>665057.6800000001</v>
+        <v>740.9</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1078078-1394-CM26</t>
+          <t>1078078-1393-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12155,11 +12155,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1046766.84</v>
+        <v>16838.09</v>
       </c>
     </row>
     <row r="193">
@@ -12216,17 +12216,17 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>813162.7</v>
+        <v>905.89</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1078078-1383-CM26</t>
+          <t>1078078-1381-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12266,28 +12266,28 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>7557322.29</v>
+        <v>149.53</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1078078-1384-CM26</t>
+          <t>1078078-1383-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -12327,28 +12327,28 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>618621.5</v>
+        <v>8419.120000000001</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1078078-1381-CM26</t>
+          <t>1078078-1384-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -12388,22 +12388,22 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>134220.1</v>
+        <v>689.17</v>
       </c>
     </row>
     <row r="197">
@@ -12460,17 +12460,17 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>404007.38</v>
+        <v>450.08</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>758-365-CM26</t>
+          <t>1079659-182-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12495,43 +12495,43 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2783326.7</v>
+        <v>9511.74</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2424-654-CM26</t>
+          <t>4562-244-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12551,48 +12551,48 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3072948.9</v>
+        <v>6348.09</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1079659-182-CM26</t>
+          <t>758-365-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,43 +12617,43 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>8538094.109999999</v>
+        <v>3100.72</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4562-244-CM26</t>
+          <t>2424-654-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12673,48 +12673,48 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>5698288.82</v>
+        <v>3423.37</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1078078-1424-CM26</t>
+          <t>1078078-1417-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12754,28 +12754,28 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>7197449.63</v>
+        <v>472.38</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1078078-1418-CM26</t>
+          <t>1078078-1421-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -12815,28 +12815,28 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1278810.89</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2427-434-CM26</t>
+          <t>1078078-1420-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12856,48 +12856,48 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>21504966</v>
+        <v>4444.29</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1078078-1419-CM26</t>
+          <t>1078078-1422-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12937,28 +12937,28 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>15107744.96</v>
+        <v>1091.39</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1078078-1422-CM26</t>
+          <t>1078078-1419-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12998,28 +12998,28 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>979673.45</v>
+        <v>16830.56</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1078078-1421-CM26</t>
+          <t>1078078-1418-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13059,28 +13059,28 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>7604124.99</v>
+        <v>1424.64</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2427-433-CM26</t>
+          <t>1078078-1423-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13105,43 +13105,43 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5639172</v>
+        <v>1602.58</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1078078-1423-CM26</t>
+          <t>2427-433-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13166,43 +13166,43 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1438541.02</v>
+        <v>6282.23</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1078078-1420-CM26</t>
+          <t>1078078-1416-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13242,28 +13242,28 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3989361.95</v>
+        <v>8673.43</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1078078-1417-CM26</t>
+          <t>1078078-1411-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13303,28 +13303,28 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>424023.18</v>
+        <v>8007.22</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1078078-1412-CM26</t>
+          <t>1078078-1414-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -13364,28 +13364,28 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>371038.43</v>
+        <v>9139.75</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1078078-1415-CM26</t>
+          <t>4451-272-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13410,43 +13410,43 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>934662.89</v>
+        <v>3046.46</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1078078-1414-CM26</t>
+          <t>1078078-1412-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13486,28 +13486,28 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>8204186.06</v>
+        <v>413.35</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4451-272-CM26</t>
+          <t>1078078-1410-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13532,43 +13532,43 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2734620</v>
+        <v>1137.1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1078078-1411-CM26</t>
+          <t>1078078-1407-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13608,28 +13608,28 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7187588.1</v>
+        <v>8415.280000000001</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1078078-1410-CM26</t>
+          <t>4105-346-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13649,48 +13649,48 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1020701.08</v>
+        <v>4820.12</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1078078-1407-CM26</t>
+          <t>316-299-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13710,48 +13710,48 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>7553872.48</v>
+        <v>12725.66</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4105-346-CM26</t>
+          <t>1078078-1424-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13771,48 +13771,48 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>4326721</v>
+        <v>8018.21</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>316-299-CM26</t>
+          <t>1078078-1415-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13832,48 +13832,48 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>11423038.48</v>
+        <v>1041.25</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1078078-1416-CM26</t>
+          <t>1078078-1406-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13913,28 +13913,28 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>7785597.61</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1078078-1406-CM26</t>
+          <t>2793-462-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13949,22 +13949,22 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,28 +13974,28 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.292.846-7</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>53231.08</v>
+        <v>9936.93</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2793-462-CM26</t>
+          <t>2380-921-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14020,43 +14020,43 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>77.292.846-7</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>8919764</v>
+        <v>41082.5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2380-921-CM26</t>
+          <t>3459-133-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14071,53 +14071,53 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>36877207.5</v>
+        <v>3443.58</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3459-133-CM26</t>
+          <t>1078078-1425-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14137,48 +14137,48 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3091084.5</v>
+        <v>1513.97</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2702-238-CM26</t>
+          <t>1078078-1426-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14218,28 +14218,28 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4069252.6</v>
+        <v>1703.36</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1078078-1433-CM26</t>
+          <t>1078078-1427-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14279,28 +14279,28 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>494683</v>
+        <v>851.21</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1078078-1431-CM26</t>
+          <t>1078078-1428-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -14340,28 +14340,28 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>639215.64</v>
+        <v>8018.21</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1078078-1430-CM26</t>
+          <t>1078078-1429-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -14401,28 +14401,28 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7604124.99</v>
+        <v>937.65</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1078078-1432-CM26</t>
+          <t>1078078-1430-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -14462,28 +14462,28 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1078078-1428-CM26</t>
+          <t>1078078-1431-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -14523,28 +14523,28 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>7197449.63</v>
+        <v>712.11</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1078078-1427-CM26</t>
+          <t>1078078-1432-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14584,28 +14584,28 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>764081.15</v>
+        <v>8619.32</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1078078-1426-CM26</t>
+          <t>1078078-1433-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14645,28 +14645,28 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1529002.44</v>
+        <v>551.09</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1078078-1425-CM26</t>
+          <t>2702-238-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14706,28 +14706,28 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1358994.28</v>
+        <v>4533.29</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1078078-1429-CM26</t>
+          <t>4956-92-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14767,28 +14767,28 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>841666.77</v>
+        <v>29919.54</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1078078-1445-CM26</t>
+          <t>1078078-1452-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14839,17 +14839,17 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2880937.64</v>
+        <v>809.98</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4956-92-CM26</t>
+          <t>1078078-1451-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14889,28 +14889,28 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>26856910.08</v>
+        <v>560.1900000000001</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1078078-1452-CM26</t>
+          <t>1078078-1447-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14961,17 +14961,17 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>727066.2</v>
+        <v>1391.31</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1078078-1451-CM26</t>
+          <t>1078078-1445-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15022,17 +15022,17 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>502847.59</v>
+        <v>3209.47</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1078078-1447-CM26</t>
+          <t>1078078-1440-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15052,7 +15052,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -15072,28 +15072,28 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1248889.53</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2111-9201-CM26</t>
+          <t>1078078-1443-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15113,17 +15113,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15133,28 +15133,28 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>14256200</v>
+        <v>8419.049999999999</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1078078-1441-CM26</t>
+          <t>1078078-1442-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15194,28 +15194,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>610702.05</v>
+        <v>6128.86</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1078078-1443-CM26</t>
+          <t>1078078-1441-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15255,28 +15255,28 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>7557254.46</v>
+        <v>680.34</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1078078-1442-CM26</t>
+          <t>3567-277-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15316,28 +15316,28 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>5501493.76</v>
+        <v>56295.87</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1078078-1440-CM26</t>
+          <t>1078078-1444-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15377,28 +15377,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>7604124.99</v>
+        <v>1068.78</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3567-277-CM26</t>
+          <t>1078078-1463-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.150.700-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FLORIDA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15438,28 +15438,28 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>50533302.4</v>
+        <v>139.67</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1078078-1444-CM26</t>
+          <t>1078078-1467-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -15499,28 +15499,28 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>959378</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1078078-1463-CM26</t>
+          <t>1078078-1464-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -15560,28 +15560,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>125377.21</v>
+        <v>361.42</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1078078-1468-CM26</t>
+          <t>1078078-1462-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15632,17 +15632,17 @@
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>809527.25</v>
+        <v>1090.85</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1078078-1464-CM26</t>
+          <t>1078078-1468-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -15682,28 +15682,28 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>324427.32</v>
+        <v>901.84</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1078078-1462-CM26</t>
+          <t>1078078-1458-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15743,28 +15743,28 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>979185.55</v>
+        <v>8419.049999999999</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1078078-1467-CM26</t>
+          <t>1078078-1457-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15804,28 +15804,28 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>7604124.99</v>
+        <v>858.64</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1078078-1458-CM26</t>
+          <t>1078078-1455-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -15865,28 +15865,28 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1078078-1457-CM26</t>
+          <t>1078078-1453-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -15926,28 +15926,28 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>770749.91</v>
+        <v>2447.31</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1078078-1455-CM26</t>
+          <t>1078078-1460-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -15987,28 +15987,28 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7604124.99</v>
+        <v>631.7</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1078078-1460-CM26</t>
+          <t>1078078-1484-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16048,28 +16048,28 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>567038.5699999999</v>
+        <v>1765.22</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1078078-1453-CM26</t>
+          <t>1078078-1483-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -16109,28 +16109,28 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2196794.74</v>
+        <v>676.34</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1078078-1484-CM26</t>
+          <t>1078078-1482-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16181,17 +16181,17 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1584527.84</v>
+        <v>2781.78</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1078078-1483-CM26</t>
+          <t>1078078-1477-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16231,28 +16231,28 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>607107.0600000001</v>
+        <v>16830.56</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1078078-1482-CM26</t>
+          <t>1078078-1478-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16303,17 +16303,17 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2497030.55</v>
+        <v>1262.58</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1078078-1477-CM26</t>
+          <t>1078078-1474-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16353,28 +16353,28 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>15107744.96</v>
+        <v>8007.22</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1078078-1478-CM26</t>
+          <t>1078078-1473-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16414,28 +16414,28 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1133339.34</v>
+        <v>16830.56</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1078078-1474-CM26</t>
+          <t>1078078-1472-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -16475,28 +16475,28 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7187588.1</v>
+        <v>590.78</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1078078-1473-CM26</t>
+          <t>1078078-1470-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16547,17 +16547,17 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>15107744.96</v>
+        <v>8415.280000000001</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1078078-1472-CM26</t>
+          <t>1078078-1476-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16608,17 +16608,17 @@
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>530305.65</v>
+        <v>676.83</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1078078-1470-CM26</t>
+          <t>1078078-1494-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -16658,28 +16658,28 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>7553872.48</v>
+        <v>1663.72</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1078078-1476-CM26</t>
+          <t>1078078-1500-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16694,7 +16694,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -16719,28 +16719,28 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>607550.9300000001</v>
+        <v>1927.97</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1078078-1494-CM26</t>
+          <t>1078078-1499-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16780,28 +16780,28 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1493414.3</v>
+        <v>16830.56</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1078078-1500-CM26</t>
+          <t>1078078-1502-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16841,28 +16841,28 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1730614.62</v>
+        <v>8619.32</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1078078-1499-CM26</t>
+          <t>1078078-1498-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16902,28 +16902,28 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>15107744.96</v>
+        <v>1187.3</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1078078-1502-CM26</t>
+          <t>1078078-1497-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16963,28 +16963,28 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>7737028.95</v>
+        <v>16830.56</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1078078-1498-CM26</t>
+          <t>1078078-1496-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17024,28 +17024,28 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1065768.76</v>
+        <v>692.26</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1078078-1497-CM26</t>
+          <t>1078078-1495-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17085,28 +17085,28 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>15107744.96</v>
+        <v>8419.049999999999</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1078078-1496-CM26</t>
+          <t>1078078-1493-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17146,28 +17146,28 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>621401.34</v>
+        <v>8419.049999999999</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1078078-1495-CM26</t>
+          <t>1078078-1485-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -17207,28 +17207,28 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8007.22</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1078078-1493-CM26</t>
+          <t>1078078-1491-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17268,28 +17268,28 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8471.26</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1078078-1485-CM26</t>
+          <t>1078078-1490-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17340,17 +17340,17 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>7187588.1</v>
+        <v>8007.22</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1078078-1491-CM26</t>
+          <t>1078078-1489-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17390,28 +17390,28 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>7604124.99</v>
+        <v>25901.79</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1078078-1490-CM26</t>
+          <t>1078078-1488-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -17451,28 +17451,28 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>7187588.1</v>
+        <v>924.3</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1078078-1489-CM26</t>
+          <t>1078078-1487-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -17512,28 +17512,28 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>23250428.25</v>
+        <v>7938.94</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1078078-1488-CM26</t>
+          <t>1078078-1486-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17573,28 +17573,28 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>829685.85</v>
+        <v>612.66</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1078078-1487-CM26</t>
+          <t>2432-325-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17614,17 +17614,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17634,28 +17634,28 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.292.846-7</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>7126297.15</v>
+        <v>501.12</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1078078-1486-CM26</t>
+          <t>3349-158-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17675,48 +17675,48 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>549950.17</v>
+        <v>21243.12</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2432-325-CM26</t>
+          <t>1078078-1503-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17741,12 +17741,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17756,28 +17756,28 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>77.292.846-7</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>449820</v>
+        <v>707.16</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3349-158-CM26</t>
+          <t>1078078-1492-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17797,48 +17797,48 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>19068626.64</v>
+        <v>922.37</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1078078-1503-CM26</t>
+          <t>1298356-33-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17858,17 +17858,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>DIRECCION DE INFANCIA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17878,144 +17878,22 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>634772.1800000001</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>1078078-1492-CM26</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>ABATTE OFFICITY</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>96.909.950-0</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M287" s="2" t="n">
-        <v>827955.59</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>1298356-33-CM26</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>71.293.900-1</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>DIRECCION DE INFANCIA</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>DIMERC S A</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M288" s="2" t="n">
-        <v>1957454.8</v>
+        <v>2180.67</v>
       </c>
     </row>
   </sheetData>
